--- a/REPORTS/RESULT_LSTM/SUMMARY_RESULTS_PORTFOLIO_LSTM_EPOCH1000.xlsx
+++ b/REPORTS/RESULT_LSTM/SUMMARY_RESULTS_PORTFOLIO_LSTM_EPOCH1000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\@@GithubTesis\FinanceV1\REPORTS\RESULT_LSTM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4FD3D4-8BB9-4687-BDD2-EE8BC9CF4013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF39F737-99AF-4E77-8DF3-C51B11FEF7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORT" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -128,7 +128,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -432,128 +432,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="B2:J5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6328125" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="13.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
+      <c r="C3">
         <v>60</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D3" s="2">
         <v>2028702.777238281</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E3" s="2">
         <v>2863400.7015608558</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F3" s="2">
         <v>1001737.0925</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G3" s="2">
         <v>1264608.232430296</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H3" s="2">
         <v>1557727.25</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I3" s="2">
         <v>1507287.875</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J3" s="2">
         <v>1562874</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
+      <c r="C4">
         <v>60</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D4" s="2">
         <v>310525.38872321427</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E4" s="2">
         <v>392581.88190647052</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F4" s="2">
         <v>1027307.8043749999</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G4" s="2">
         <v>1401665.1758220801</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H4" s="2">
         <v>433113.5</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I4" s="2">
         <v>439415.34375</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J4" s="2">
         <v>438733.3125</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
+      <c r="C5">
         <v>36</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D5" s="2">
         <v>32589.008257812511</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E5" s="2">
         <v>35362.177560209508</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F5" s="2">
         <v>96695.125507812496</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G5" s="2">
         <v>116377.4087081084</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H5" s="2">
         <v>70075.4453125</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I5" s="2">
         <v>67023.9296875</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J5" s="2">
         <v>30187.21875</v>
       </c>
     </row>
